--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487608_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487608_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. REDONDO ALVAREZ DE SOTOMAYOR</t>
+          <t>A. VIDAL RODRIGUEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.189</v>
+        <v>2.7249</v>
       </c>
       <c r="E2" t="n">
-        <v>2.5931</v>
+        <v>2.4487</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5959</v>
+        <v>0.2762</v>
       </c>
       <c r="G2" t="n">
-        <v>1.6249</v>
+        <v>3.8741</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6089</v>
+        <v>3.943</v>
       </c>
       <c r="I2" t="n">
-        <v>1.016</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>1.8383</v>
+        <v>3.5744</v>
       </c>
       <c r="K2" t="n">
-        <v>1.067</v>
+        <v>3.4932</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7713</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.2134</v>
+        <v>0.2996</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.4581</v>
+        <v>0.4498</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2447</v>
+        <v>-0.1502</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.1642</v>
+        <v>-0.5821</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.5224</v>
+        <v>-0.9702</v>
       </c>
       <c r="R2" t="n">
-        <v>1.3582</v>
+        <v>0.3881</v>
       </c>
       <c r="S2" t="n">
-        <v>3.0686</v>
+        <v>0.3269</v>
       </c>
       <c r="T2" t="n">
-        <v>3.2772</v>
+        <v>0.5041</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2086</v>
+        <v>-0.1772</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6597</v>
+        <v>-0.894</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>-0.6597</v>
       </c>
       <c r="X2" t="n">
-        <v>0.6597</v>
+        <v>-0.2343</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. VIDAL RODRIGUEZ</t>
+          <t>A. SANTANA OJEDA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5375</v>
+        <v>2.5405</v>
       </c>
       <c r="E3" t="n">
-        <v>2.9887</v>
+        <v>2.5713</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5488</v>
+        <v>-0.0308</v>
       </c>
       <c r="G3" t="n">
-        <v>3.8741</v>
+        <v>4.0997</v>
       </c>
       <c r="H3" t="n">
-        <v>3.943</v>
+        <v>1.9303</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.06900000000000001</v>
+        <v>2.1694</v>
       </c>
       <c r="J3" t="n">
-        <v>3.5744</v>
+        <v>4.1682</v>
       </c>
       <c r="K3" t="n">
-        <v>3.4932</v>
+        <v>1.7095</v>
       </c>
       <c r="L3" t="n">
-        <v>0.08119999999999999</v>
+        <v>2.4586</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2996</v>
+        <v>-0.0684</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4498</v>
+        <v>0.2208</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.1502</v>
+        <v>-0.2892</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.5821</v>
+        <v>-0.7761</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9702</v>
+        <v>-1.5523</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3881</v>
+        <v>0.7761</v>
       </c>
       <c r="S3" t="n">
-        <v>1.1395</v>
+        <v>-0.7831</v>
       </c>
       <c r="T3" t="n">
-        <v>1.0442</v>
+        <v>-0.0446</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0954</v>
+        <v>-0.7385</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.894</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.6597</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2343</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. SANTANA OJEDA</t>
+          <t>A. REDONDO ALVAREZ DE SOTOMAYOR</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0067</v>
+        <v>1.7748</v>
       </c>
       <c r="E4" t="n">
-        <v>2.0102</v>
+        <v>0.4515</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0036</v>
+        <v>1.3234</v>
       </c>
       <c r="G4" t="n">
-        <v>4.0997</v>
+        <v>1.6249</v>
       </c>
       <c r="H4" t="n">
-        <v>1.9303</v>
+        <v>0.6089</v>
       </c>
       <c r="I4" t="n">
-        <v>2.1694</v>
+        <v>1.016</v>
       </c>
       <c r="J4" t="n">
-        <v>4.1682</v>
+        <v>1.8383</v>
       </c>
       <c r="K4" t="n">
-        <v>1.7095</v>
+        <v>1.067</v>
       </c>
       <c r="L4" t="n">
-        <v>2.4586</v>
+        <v>0.7713</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.0684</v>
+        <v>-0.2134</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2208</v>
+        <v>-0.4581</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2892</v>
+        <v>0.2447</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.7761</v>
+        <v>-1.1642</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.5523</v>
+        <v>-2.5224</v>
       </c>
       <c r="R4" t="n">
-        <v>0.7761</v>
+        <v>1.3582</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.3169</v>
+        <v>0.6544</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6057</v>
+        <v>1.1356</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.7113</v>
+        <v>-0.4811</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.6597</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>0.6597</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2756</v>
+        <v>1.4368</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3819</v>
+        <v>1.2433</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1063</v>
+        <v>0.1935</v>
       </c>
       <c r="G5" t="n">
         <v>2.5197</v>
@@ -844,13 +844,13 @@
         <v>1.1642</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9038</v>
+        <v>0.2574</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5328000000000001</v>
+        <v>0.3286</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.371</v>
+        <v>-0.0712</v>
       </c>
       <c r="V5" t="n">
         <v>-0.5642</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1792</v>
+        <v>0.8949</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3294</v>
+        <v>0.3317</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5087</v>
+        <v>0.5632</v>
       </c>
       <c r="G6" t="n">
         <v>-0.6284</v>
@@ -922,13 +922,13 @@
         <v>1.5523</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.1043</v>
+        <v>-0.3886</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4722</v>
+        <v>0.189</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6321</v>
+        <v>-0.5776</v>
       </c>
       <c r="V6" t="n">
         <v>0.9418</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0318</v>
+        <v>0.7197</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2186</v>
+        <v>0.1423</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2504</v>
+        <v>0.5774</v>
       </c>
       <c r="G7" t="n">
         <v>0.7716</v>
@@ -1000,13 +1000,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7398</v>
+        <v>-0.0519</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.424</v>
+        <v>-0.0631</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3158</v>
+        <v>0.0112</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1314</v>
+        <v>-0.052</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0014</v>
+        <v>-0.5404</v>
       </c>
       <c r="F8" t="n">
-        <v>0.87</v>
+        <v>0.4884</v>
       </c>
       <c r="G8" t="n">
         <v>0.2463</v>
@@ -1078,13 +1078,13 @@
         <v>0.9702</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0104</v>
+        <v>0.0897</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.12</v>
+        <v>0.3409</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1304</v>
+        <v>-0.2512</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9847</v>
+        <v>-1.215</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.8806</v>
+        <v>-1.9201</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8959</v>
+        <v>0.7050999999999999</v>
       </c>
       <c r="G9" t="n">
         <v>-2.1826</v>
@@ -1156,13 +1156,13 @@
         <v>1.3582</v>
       </c>
       <c r="S9" t="n">
-        <v>1.0606</v>
+        <v>0.8303</v>
       </c>
       <c r="T9" t="n">
-        <v>0.6808</v>
+        <v>0.6412</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3798</v>
+        <v>0.189</v>
       </c>
       <c r="V9" t="n">
         <v>1.8836</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.3899</v>
+        <v>-1.2505</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.4035</v>
+        <v>-1.7819</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0136</v>
+        <v>0.5314</v>
       </c>
       <c r="G10" t="n">
         <v>1.2093</v>
@@ -1234,13 +1234,13 @@
         <v>1.3582</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.3887</v>
+        <v>-0.2493</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2288</v>
+        <v>0.3928</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.1599</v>
+        <v>-0.6421</v>
       </c>
       <c r="V10" t="n">
         <v>0.894</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.2826</v>
+        <v>-3.5373</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.5512</v>
+        <v>-1.7514</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.7313</v>
+        <v>-1.7858</v>
       </c>
       <c r="G11" t="n">
         <v>-0.0725</v>
@@ -1312,13 +1312,13 @@
         <v>0.7761</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1339</v>
+        <v>-0.3886</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3645</v>
+        <v>0.1643</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4984</v>
+        <v>-0.5528999999999999</v>
       </c>
       <c r="V11" t="n">
         <v>-0.9418</v>
@@ -1345,19 +1345,19 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.431199999999998</v>
+        <v>4.0368</v>
       </c>
       <c r="E12" t="n">
-        <v>0.5892000000000006</v>
+        <v>1.195</v>
       </c>
       <c r="F12" t="n">
-        <v>2.842100000000001</v>
+        <v>2.842</v>
       </c>
       <c r="G12" t="n">
         <v>11.4621</v>
       </c>
       <c r="H12" t="n">
-        <v>6.846399999999999</v>
+        <v>6.846400000000001</v>
       </c>
       <c r="I12" t="n">
         <v>4.615500000000001</v>
@@ -1390,13 +1390,13 @@
         <v>9.701599999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3083000000000001</v>
+        <v>0.2972000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>2.983200000000001</v>
+        <v>3.5888</v>
       </c>
       <c r="U12" t="n">
-        <v>-3.2915</v>
+        <v>-3.2916</v>
       </c>
       <c r="V12" t="n">
         <v>1.9791</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.4866</v>
+        <v>3.9452</v>
       </c>
       <c r="E13" t="n">
-        <v>4.7882</v>
+        <v>2.7862</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6984</v>
+        <v>1.159</v>
       </c>
       <c r="G13" t="n">
         <v>3.2148</v>
@@ -1468,13 +1468,13 @@
         <v>3.1045</v>
       </c>
       <c r="S13" t="n">
-        <v>2.3793</v>
+        <v>0.8378</v>
       </c>
       <c r="T13" t="n">
-        <v>2.999</v>
+        <v>0.997</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6198</v>
+        <v>-0.1592</v>
       </c>
       <c r="V13" t="n">
         <v>-1.2716</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.2362</v>
+        <v>2.0431</v>
       </c>
       <c r="E14" t="n">
-        <v>2.0224</v>
+        <v>2.7231</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.7862</v>
+        <v>-0.68</v>
       </c>
       <c r="G14" t="n">
         <v>1.1133</v>
@@ -1546,13 +1546,13 @@
         <v>3.2985</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.5756</v>
+        <v>0.2313</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5193</v>
+        <v>0.1814</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0563</v>
+        <v>0.0499</v>
       </c>
       <c r="V14" t="n">
         <v>-0.6597</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4676</v>
+        <v>0.9648</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.5177</v>
+        <v>-0.3175</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9854000000000001</v>
+        <v>1.2824</v>
       </c>
       <c r="G15" t="n">
         <v>0.4124</v>
@@ -1624,13 +1624,13 @@
         <v>2.3284</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.897</v>
+        <v>-0.3998</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2288</v>
+        <v>-0.0286</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6682</v>
+        <v>-0.3712</v>
       </c>
       <c r="V15" t="n">
         <v>0.5642</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. LARREA IBARBURU</t>
+          <t>O. BALSELLS PLAZA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3119</v>
+        <v>0.0329</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.5264</v>
+        <v>-0.844</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8383</v>
+        <v>0.8768</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.0286</v>
+        <v>-2.4197</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.6314</v>
+        <v>0.337</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6028</v>
+        <v>-2.7566</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.0255</v>
+        <v>-1.1879</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.6395</v>
+        <v>0.7456</v>
       </c>
       <c r="L16" t="n">
-        <v>0.614</v>
+        <v>-1.9335</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.0031</v>
+        <v>-1.2317</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.992</v>
+        <v>-0.4087</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.0111</v>
+        <v>-0.8231000000000001</v>
       </c>
       <c r="P16" t="n">
-        <v>1.3582</v>
+        <v>0.7761</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.9403</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3582</v>
+        <v>2.7164</v>
       </c>
       <c r="S16" t="n">
-        <v>0.9823</v>
+        <v>0.1705</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4991</v>
+        <v>0.7783</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4832</v>
+        <v>-0.6079</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.506</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.506</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. VIERA LOPEZ</t>
+          <t>J. LARREA IBARBURU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.9231</v>
+        <v>-0.4912</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.6421</v>
+        <v>-1.0269</v>
       </c>
       <c r="F17" t="n">
-        <v>0.719</v>
+        <v>0.5357</v>
       </c>
       <c r="G17" t="n">
-        <v>-3.5797</v>
+        <v>-2.0286</v>
       </c>
       <c r="H17" t="n">
-        <v>-3.6497</v>
+        <v>-2.6314</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0701</v>
+        <v>0.6028</v>
       </c>
       <c r="J17" t="n">
-        <v>-2.287</v>
+        <v>-1.0255</v>
       </c>
       <c r="K17" t="n">
-        <v>-3.1801</v>
+        <v>-1.6395</v>
       </c>
       <c r="L17" t="n">
-        <v>0.8931</v>
+        <v>0.614</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.2927</v>
+        <v>-1.0031</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4696</v>
+        <v>-0.992</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.8231000000000001</v>
+        <v>-0.0111</v>
       </c>
       <c r="P17" t="n">
-        <v>2.7164</v>
+        <v>1.3582</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.7164</v>
+        <v>1.3582</v>
       </c>
       <c r="S17" t="n">
-        <v>0.552</v>
+        <v>0.1792</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6449</v>
+        <v>-0.0014</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.09279999999999999</v>
+        <v>0.1806</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.6119</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.6119</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>O. BALSELLS PLAZA</t>
+          <t>D. VIERA LOPEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9859</v>
+        <v>-0.768</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.6448</v>
+        <v>-1.2417</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6588000000000001</v>
+        <v>0.4737</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.4197</v>
+        <v>-3.5797</v>
       </c>
       <c r="H18" t="n">
-        <v>0.337</v>
+        <v>-3.6497</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.7566</v>
+        <v>0.0701</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.1879</v>
+        <v>-2.287</v>
       </c>
       <c r="K18" t="n">
-        <v>0.7456</v>
+        <v>-3.1801</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.9335</v>
+        <v>0.8931</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.2317</v>
+        <v>-1.2927</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4087</v>
+        <v>-0.4696</v>
       </c>
       <c r="O18" t="n">
         <v>-0.8231000000000001</v>
       </c>
       <c r="P18" t="n">
-        <v>0.7761</v>
+        <v>2.7164</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9403</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>2.7164</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8484</v>
+        <v>0.7071</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0225</v>
+        <v>1.0453</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.8259</v>
+        <v>-0.3381</v>
       </c>
       <c r="V18" t="n">
-        <v>1.506</v>
+        <v>-0.6119</v>
       </c>
       <c r="W18" t="n">
-        <v>1.506</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.6119</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.852</v>
+        <v>-1.3426</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4236</v>
+        <v>-1.0232</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4284</v>
+        <v>-0.3194</v>
       </c>
       <c r="G19" t="n">
         <v>-2.398</v>
@@ -1936,13 +1936,13 @@
         <v>1.3582</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8122</v>
+        <v>-0.3028</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2176</v>
+        <v>0.1828</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5946</v>
+        <v>-0.4856</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.9968</v>
+        <v>-1.7538</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.5918</v>
+        <v>-1.2915</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.405</v>
+        <v>-0.4623</v>
       </c>
       <c r="G20" t="n">
         <v>-1.8421</v>
@@ -2014,13 +2014,13 @@
         <v>1.5523</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4547</v>
+        <v>-0.2117</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3623</v>
+        <v>-0.062</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0924</v>
+        <v>-0.1497</v>
       </c>
       <c r="V20" t="n">
         <v>-0.2821</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.1756</v>
+        <v>-5.3942</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.3061</v>
+        <v>-2.6064</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.8695</v>
+        <v>-2.7878</v>
       </c>
       <c r="G21" t="n">
         <v>-3.9345</v>
@@ -2092,13 +2092,13 @@
         <v>0.9702</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0173</v>
+        <v>-0.2358</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4991</v>
+        <v>0.1988</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5164</v>
+        <v>-0.4346</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2239</v>
@@ -2125,19 +2125,19 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.4311</v>
+        <v>-2.7638</v>
       </c>
       <c r="E22" t="n">
         <v>-2.841900000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.5891999999999999</v>
+        <v>0.07810000000000006</v>
       </c>
       <c r="G22" t="n">
         <v>-11.4621</v>
       </c>
       <c r="H22" t="n">
-        <v>-6.846400000000001</v>
+        <v>-6.846399999999999</v>
       </c>
       <c r="I22" t="n">
         <v>-4.615600000000001</v>
@@ -2158,25 +2158,25 @@
         <v>-7.3081</v>
       </c>
       <c r="O22" t="n">
-        <v>-6.173100000000001</v>
+        <v>-6.1731</v>
       </c>
       <c r="P22" t="n">
         <v>9.701500000000001</v>
       </c>
       <c r="Q22" t="n">
-        <v>-9.701600000000001</v>
+        <v>-9.701599999999999</v>
       </c>
       <c r="R22" t="n">
         <v>19.4031</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3083999999999999</v>
+        <v>0.9758</v>
       </c>
       <c r="T22" t="n">
-        <v>3.2916</v>
+        <v>3.291599999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>-2.9832</v>
+        <v>-2.3158</v>
       </c>
       <c r="V22" t="n">
         <v>-1.979</v>
